--- a/PA2/PA2Data.xlsx
+++ b/PA2/PA2Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Doc\School\SDSU\COMPE571\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D2BEC29-1D17-491D-B37B-E11061199FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABEE734D-77F3-4F19-AAB8-AA7BF560AF96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{691951DA-07BF-4159-BB9F-3D5029AFADA7}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{691951DA-07BF-4159-BB9F-3D5029AFADA7}"/>
   </bookViews>
   <sheets>
     <sheet name="FCFS" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="22">
   <si>
     <t>P1 Response</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>Average Context Switch Time(ms)</t>
   </si>
 </sst>
 </file>
@@ -197,7 +200,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -209,6 +212,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -10228,7 +10240,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EACC7A2C-CA60-4C06-AB4D-3754840E7F1A}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10359,8 +10371,70 @@
         <v>7.5024999999999967E-2</v>
       </c>
     </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="8">
+        <f>FCFS!H103*1000</f>
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="9">
+        <f>MLFQ!E104*1000</f>
+        <v>2.5500000000000043E-2</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="8">
+        <f>RR!E104*1000</f>
+        <v>17.858699999999992</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="9">
+        <f>SJF!H104*1000</f>
+        <v>7.000000000000001E-4</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="6">
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B13:E13"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
